--- a/tools/excel_export/excel/units.xlsx
+++ b/tools/excel_export/excel/units.xlsx
@@ -181,7 +181,7 @@
     <t>1:320|2:120|3:40|4:120|16:350</t>
   </si>
   <si>
-    <t>12,16</t>
+    <t>16</t>
   </si>
   <si>
     <t>farthest</t>
@@ -250,7 +250,7 @@
     <t>1:560|2:80|3:34|4:100|16:200</t>
   </si>
   <si>
-    <t>17,18</t>
+    <t>17</t>
   </si>
   <si>
     <t>prefabs/units/hero_axe</t>

--- a/tools/excel_export/excel/units.xlsx
+++ b/tools/excel_export/excel/units.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="164">
   <si>
     <t>id</t>
   </si>
@@ -154,7 +154,7 @@
     <t>击杀经验基数（缺省取 battle_constants.enemyDropExpDefault）</t>
   </si>
   <si>
-    <t>奖励类型（gold_boss/exp_boss 为经济BOSS）</t>
+    <t>奖励类型（gold_boss/exp_boss 为经济BOSS，kill_boss 为击杀BOSS）</t>
   </si>
   <si>
     <t>AI 配置 JSON：{"type":"chase","params":{...}}</t>
@@ -178,7 +178,7 @@
     <t>hero</t>
   </si>
   <si>
-    <t>1:320|2:120|3:40|4:120|16:350</t>
+    <t>1:320|2:120|3:40|4:120|16:250</t>
   </si>
   <si>
     <t>16</t>
@@ -226,7 +226,7 @@
     <t>textures/heros/zhousi</t>
   </si>
   <si>
-    <t>1:340|2:220|3:26|4:100|16:600</t>
+    <t>1:340|2:220|3:26|4:100|16:250</t>
   </si>
   <si>
     <t>19</t>
@@ -247,7 +247,7 @@
     <t>textures/heros/fuwang</t>
   </si>
   <si>
-    <t>1:560|2:80|3:34|4:100|16:200</t>
+    <t>1:560|2:80|3:34|4:100|16:187</t>
   </si>
   <si>
     <t>17</t>
@@ -259,6 +259,120 @@
     <t>1:22|3:1.5</t>
   </si>
   <si>
+    <t>幻影刺客</t>
+  </si>
+  <si>
+    <t>textures/heros/huanci</t>
+  </si>
+  <si>
+    <t>1:300|2:100|3:44|4:110|16:187</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>nearest</t>
+  </si>
+  <si>
+    <t>1:11|3:3.2</t>
+  </si>
+  <si>
+    <t>卓尔游侠</t>
+  </si>
+  <si>
+    <t>textures/heros/zhuoer</t>
+  </si>
+  <si>
+    <t>1:300|2:120|3:32|4:140|16:240</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>lowest_hp</t>
+  </si>
+  <si>
+    <t>arrow</t>
+  </si>
+  <si>
+    <t>1:11|3:2.6</t>
+  </si>
+  <si>
+    <t>水晶室女</t>
+  </si>
+  <si>
+    <t>textures/heros/shuijing</t>
+  </si>
+  <si>
+    <t>1:420|2:260|3:24|4:100|16:240</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>ice</t>
+  </si>
+  <si>
+    <t>1:16|2:12|3:1.8</t>
+  </si>
+  <si>
+    <t>莉娜</t>
+  </si>
+  <si>
+    <t>textures/heros/lina</t>
+  </si>
+  <si>
+    <t>1:320|2:200|3:30|4:105|16:250</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>strongest</t>
+  </si>
+  <si>
+    <t>fire</t>
+  </si>
+  <si>
+    <t>1:12|2:10|3:2.4</t>
+  </si>
+  <si>
+    <t>冥界亚龙</t>
+  </si>
+  <si>
+    <t>textures/heros/viper</t>
+  </si>
+  <si>
+    <t>1:380|2:160|3:28|4:120|16:220</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>venom</t>
+  </si>
+  <si>
+    <t>1:14|3:2.2</t>
+  </si>
+  <si>
+    <t>谜团</t>
+  </si>
+  <si>
+    <t>textures/heros/mituan</t>
+  </si>
+  <si>
+    <t>1:400|2:240|3:26|4:95|16:220</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>shadow</t>
+  </si>
+  <si>
+    <t>1:15|2:11|3:2</t>
+  </si>
+  <si>
     <t>哥布林</t>
   </si>
   <si>
@@ -298,7 +412,7 @@
     <t>1:80|2:20|5:140|3:7|4:100|6:0|7:20|16:90</t>
   </si>
   <si>
-    <t>{"type":"wander","params":{"wanderRadius":150,"aggroRange":350,"wanderSpeedMul":0.5,"chaseSpeedMul":1.1}}</t>
+    <t>{"type":"wander","params":{"wanderRadius":150,"aggroRange":350,"wanderSpeedMul":0.5,"chaseSpeedMul":1.1,"aggroAfter":5}}</t>
   </si>
   <si>
     <t>prefabs/units/monster_6</t>
@@ -310,7 +424,7 @@
     <t>1:90|2:40|5:180|3:6|4:100|6:0|7:30|16:120</t>
   </si>
   <si>
-    <t>{"type":"orbit","params":{"orbitRadius":200,"angularSpeed":1.8,"attackInterval":2.5}}</t>
+    <t>{"type":"orbit","params":{"orbitRadius":150,"angularSpeed":1.8,"attackInterval":2.5}}</t>
   </si>
   <si>
     <t>prefabs/units/monster_7</t>
@@ -343,7 +457,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>{"type":"boss","params":{"skillInterval":6,"skillId":"fireball","phases":[{"hpRatio":1,"behavior":"chase","params":{"speedMul":0.8}},{"hpRatio":0.7,"behavior":"orbit","params":{"orbitRadius":220,"angularSpeed":1.2}},{"hpRatio":0.4,"behavior":"chase","params":{"speedMul":1.6}},{"hpRatio":0.2,"behavior":"attack_stop","params":{"stopDuration":1.2,"speedMul":1.8}}]}}</t>
+    <t>{"type":"boss","params":{"skillInterval":6,"skillId":"fireball","phases":[{"hpRatio":1,"behavior":"chase","params":{"speedMul":0.8}},{"hpRatio":0.7,"behavior":"orbit","params":{"orbitRadius":150,"angularSpeed":1.2}},{"hpRatio":0.4,"behavior":"chase","params":{"speedMul":1.6}},{"hpRatio":0.2,"behavior":"attack_stop","params":{"stopDuration":1.2,"speedMul":1.8}}]}}</t>
   </si>
   <si>
     <t>prefabs/units/monster_9</t>
@@ -352,7 +466,7 @@
     <t>黄金魔像</t>
   </si>
   <si>
-    <t>1:2200|2:60|5:85|3:30|4:40|6:4|7:20|16:120</t>
+    <t>1:1400|2:60|5:85|3:10|4:40|6:4|7:20|16:120</t>
   </si>
   <si>
     <t>gold_boss</t>
@@ -371,6 +485,24 @@
   </si>
   <si>
     <t>{"type":"boss","params":{"skillInterval":8,"skillId":"sun_light","phases":[{"hpRatio":1,"behavior":"chase","params":{"speedMul":0.7}}]}}</t>
+  </si>
+  <si>
+    <t>处刑者</t>
+  </si>
+  <si>
+    <t>1:1800|2:100|5:150|3:55|4:100|6:6|7:25|16:180</t>
+  </si>
+  <si>
+    <t>kill_boss</t>
+  </si>
+  <si>
+    <t>{"type":"chase","params":{"speedMul":1}}</t>
+  </si>
+  <si>
+    <t>敌方守卫</t>
+  </si>
+  <si>
+    <t>1:1500|2:80|5:55|3:12|4:100|6:10|7:30|16:150</t>
   </si>
 </sst>
 </file>
@@ -810,7 +942,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18.5" customWidth="1"/>
@@ -830,7 +962,7 @@
     <col min="15" max="15" width="10" customWidth="1"/>
     <col min="16" max="16" width="30" customWidth="1"/>
     <col min="17" max="17" width="29.5" customWidth="1"/>
-    <col min="18" max="18" width="20.5" customWidth="1"/>
+    <col min="18" max="18" width="31.5" customWidth="1"/>
     <col min="19" max="19" width="60" customWidth="1"/>
     <col min="20" max="20" width="18" customWidth="1"/>
     <col min="21" max="21" width="27" customWidth="1"/>
@@ -1249,435 +1381,851 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
-        <v>2001</v>
+        <v>1005</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C8" s="4"/>
+      <c r="C8" s="4" t="s">
+        <v>83</v>
+      </c>
       <c r="D8" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="F8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="H8" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>86</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4">
-        <v>2</v>
-      </c>
-      <c r="K8" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>86</v>
+      </c>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
       <c r="O8" s="4">
-        <v>50</v>
-      </c>
-      <c r="P8" s="4">
-        <v>2</v>
-      </c>
-      <c r="Q8" s="4">
-        <v>8</v>
-      </c>
-      <c r="R8" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="S8" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4">
+        <v>24</v>
+      </c>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="T8" s="4">
-        <v>10</v>
-      </c>
-      <c r="U8" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="V8" s="4"/>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
-        <v>2002</v>
+        <v>1006</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="C9" s="4"/>
       <c r="D9" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>84</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
         <v>90</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="I9" s="4"/>
       <c r="J9" s="4">
-        <v>2</v>
-      </c>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
+        <v>0.9</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>93</v>
+      </c>
       <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
+      <c r="N9" s="4" t="s">
+        <v>59</v>
+      </c>
       <c r="O9" s="4">
-        <v>80</v>
-      </c>
-      <c r="P9" s="4">
-        <v>4</v>
-      </c>
-      <c r="Q9" s="4">
-        <v>15</v>
-      </c>
-      <c r="R9" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="S9" s="4" t="s">
-        <v>91</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
       <c r="T9" s="4">
         <v>24</v>
       </c>
-      <c r="U9" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="V9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
-        <v>2003</v>
+        <v>1007</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C10" s="4"/>
+        <v>95</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>96</v>
+      </c>
       <c r="D10" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>84</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="F10" s="4"/>
       <c r="G10" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4">
-        <v>2</v>
-      </c>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
+        <v>1.3</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>99</v>
+      </c>
       <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
+      <c r="N10" s="4" t="s">
+        <v>59</v>
+      </c>
       <c r="O10" s="4">
-        <v>40</v>
-      </c>
-      <c r="P10" s="4">
-        <v>2</v>
-      </c>
-      <c r="Q10" s="4">
-        <v>6</v>
-      </c>
-      <c r="R10" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="S10" s="4" t="s">
-        <v>95</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
       <c r="T10" s="4">
-        <v>18</v>
-      </c>
-      <c r="U10" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="V10" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
-        <v>2004</v>
+        <v>1008</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="C11" s="4"/>
+        <v>101</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>102</v>
+      </c>
       <c r="D11" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>84</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="F11" s="4"/>
       <c r="G11" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4">
-        <v>2</v>
-      </c>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
+        <v>1.15</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>106</v>
+      </c>
       <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
+      <c r="N11" s="4" t="s">
+        <v>59</v>
+      </c>
       <c r="O11" s="4">
-        <v>60</v>
-      </c>
-      <c r="P11" s="4">
-        <v>3</v>
-      </c>
-      <c r="Q11" s="4">
-        <v>10</v>
-      </c>
-      <c r="R11" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="S11" s="4" t="s">
-        <v>99</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
       <c r="T11" s="4">
-        <v>18</v>
-      </c>
-      <c r="U11" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="V11" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="U11" s="4"/>
+      <c r="V11" s="4" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
-        <v>2005</v>
+        <v>1009</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C12" s="4"/>
+        <v>108</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>109</v>
+      </c>
       <c r="D12" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>102</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="F12" s="4"/>
       <c r="G12" s="4" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4">
-        <v>3</v>
-      </c>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
+        <v>1.1</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>112</v>
+      </c>
       <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
+      <c r="N12" s="4" t="s">
+        <v>59</v>
+      </c>
       <c r="O12" s="4">
-        <v>100</v>
-      </c>
-      <c r="P12" s="4">
-        <v>6</v>
-      </c>
-      <c r="Q12" s="4">
-        <v>25</v>
-      </c>
-      <c r="R12" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="S12" s="4" t="s">
-        <v>104</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
       <c r="T12" s="4">
         <v>26</v>
       </c>
-      <c r="U12" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="V12" s="4"/>
+      <c r="U12" s="4"/>
+      <c r="V12" s="4" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
-        <v>2006</v>
+        <v>1010</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="C13" s="4"/>
+        <v>114</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>115</v>
+      </c>
       <c r="D13" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>107</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="F13" s="4"/>
       <c r="G13" s="4" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="I13" s="4"/>
       <c r="J13" s="4">
-        <v>2.5</v>
-      </c>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
+        <v>1.35</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>118</v>
+      </c>
       <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
+      <c r="N13" s="4" t="s">
+        <v>59</v>
+      </c>
       <c r="O13" s="4">
-        <v>500</v>
-      </c>
-      <c r="P13" s="4">
-        <v>40</v>
-      </c>
-      <c r="Q13" s="4">
-        <v>200</v>
-      </c>
-      <c r="R13" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="S13" s="4" t="s">
-        <v>110</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4"/>
       <c r="T13" s="4">
-        <v>40</v>
-      </c>
-      <c r="U13" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="V13" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="U13" s="4"/>
+      <c r="V13" s="4" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4">
         <v>2</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
       <c r="O14" s="4">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="P14" s="4">
-        <v>250</v>
+        <v>2</v>
       </c>
       <c r="Q14" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="T14" s="4">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="U14" s="4" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="V14" s="4"/>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
-        <v>2008</v>
+        <v>2002</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4">
         <v>2</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
       <c r="O15" s="4">
+        <v>80</v>
+      </c>
+      <c r="P15" s="4">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>15</v>
+      </c>
+      <c r="R15" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="S15" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="T15" s="4">
+        <v>24</v>
+      </c>
+      <c r="U15" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="V15" s="4"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>2003</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4">
+        <v>2</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4">
+        <v>2</v>
+      </c>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4">
+        <v>40</v>
+      </c>
+      <c r="P16" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>6</v>
+      </c>
+      <c r="R16" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="S16" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="T16" s="4">
+        <v>18</v>
+      </c>
+      <c r="U16" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="V16" s="4"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>2004</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4">
+        <v>2</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4">
+        <v>2</v>
+      </c>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4">
+        <v>60</v>
+      </c>
+      <c r="P17" s="4">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>10</v>
+      </c>
+      <c r="R17" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="S17" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="T17" s="4">
+        <v>18</v>
+      </c>
+      <c r="U17" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V17" s="4"/>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>2005</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4">
+        <v>2</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4">
+        <v>3</v>
+      </c>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4">
         <v>100</v>
       </c>
-      <c r="P15" s="4">
+      <c r="P18" s="4">
+        <v>6</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>25</v>
+      </c>
+      <c r="R18" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="S18" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="T18" s="4">
+        <v>26</v>
+      </c>
+      <c r="U18" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="V18" s="4"/>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <v>2006</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4">
+        <v>2</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4">
+        <v>500</v>
+      </c>
+      <c r="P19" s="4">
+        <v>40</v>
+      </c>
+      <c r="Q19" s="4">
+        <v>200</v>
+      </c>
+      <c r="R19" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="S19" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="T19" s="4">
+        <v>40</v>
+      </c>
+      <c r="U19" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="V19" s="4"/>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>2007</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4">
+        <v>2</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4">
+        <v>2.2</v>
+      </c>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="4"/>
+      <c r="O20" s="4">
+        <v>300</v>
+      </c>
+      <c r="P20" s="4">
+        <v>60</v>
+      </c>
+      <c r="Q20" s="4">
+        <v>5</v>
+      </c>
+      <c r="R20" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="S20" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="T20" s="4">
+        <v>38</v>
+      </c>
+      <c r="U20" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="V20" s="4"/>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <v>2008</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4">
+        <v>2</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4">
+        <v>2.4</v>
+      </c>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="4"/>
+      <c r="N21" s="4"/>
+      <c r="O21" s="4">
+        <v>100</v>
+      </c>
+      <c r="P21" s="4">
         <v>1</v>
       </c>
-      <c r="Q15" s="4">
+      <c r="Q21" s="4">
         <v>800</v>
       </c>
-      <c r="R15" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="S15" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="T15" s="4">
+      <c r="R21" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="S21" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="T21" s="4">
         <v>36</v>
       </c>
-      <c r="U15" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="V15" s="4"/>
+      <c r="U21" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="V21" s="4"/>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <v>2009</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4">
+        <v>2</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4">
+        <v>2</v>
+      </c>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="4"/>
+      <c r="O22" s="4">
+        <v>400</v>
+      </c>
+      <c r="P22" s="4">
+        <v>30</v>
+      </c>
+      <c r="Q22" s="4">
+        <v>120</v>
+      </c>
+      <c r="R22" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="S22" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="T22" s="4">
+        <v>32</v>
+      </c>
+      <c r="U22" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="V22" s="4"/>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
+        <v>2010</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4">
+        <v>2</v>
+      </c>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="4"/>
+      <c r="N23" s="4"/>
+      <c r="O23" s="4">
+        <v>600</v>
+      </c>
+      <c r="P23" s="4">
+        <v>80</v>
+      </c>
+      <c r="Q23" s="4">
+        <v>200</v>
+      </c>
+      <c r="R23" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="S23" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="T23" s="4">
+        <v>48</v>
+      </c>
+      <c r="U23" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="V23" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="4">
@@ -1690,8 +2238,8 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="取值非法" error="只能是：nearest / farthest / lowest_hp / strongest / random" sqref="K4:K160">
       <formula1>"nearest,farthest,lowest_hp,strongest,random"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="取值非法" error="只能是：normal / elite / boss / gold_boss / exp_boss" sqref="R4:R160">
-      <formula1>"normal,elite,boss,gold_boss,exp_boss"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="取值非法" error="只能是：normal / elite / boss / gold_boss / exp_boss / kill_boss" sqref="R4:R160">
+      <formula1>"normal,elite,boss,gold_boss,exp_boss,kill_boss"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tools/excel_export/excel/units.xlsx
+++ b/tools/excel_export/excel/units.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="166">
   <si>
     <t>id</t>
   </si>
@@ -64,6 +64,9 @@
     <t>expReward</t>
   </si>
   <si>
+    <t>killReward</t>
+  </si>
+  <si>
     <t>rewardType</t>
   </si>
   <si>
@@ -154,6 +157,9 @@
     <t>击杀经验基数（缺省取 battle_constants.enemyDropExpDefault）</t>
   </si>
   <si>
+    <t>击杀数奖励（击杀商店的货币；每杀该单位给几点，缺省 1）。玩家自己放的「击杀怪」（rewardType=kill_boss）靠这一列给一次性大额</t>
+  </si>
+  <si>
     <t>奖励类型（gold_boss/exp_boss 为经济BOSS，kill_boss 为击杀BOSS）</t>
   </si>
   <si>
@@ -205,7 +211,7 @@
     <t>textures/heros/shangjin</t>
   </si>
   <si>
-    <t>1:520|2:100|3:200|4:120|16:200</t>
+    <t>1:520|2:100|3:24|4:120|16:200</t>
   </si>
   <si>
     <t>7</t>
@@ -283,7 +289,7 @@
     <t>textures/heros/zhuoer</t>
   </si>
   <si>
-    <t>1:300|2:120|3:32|4:140|16:240</t>
+    <t>1:300|2:120|3:38|4:140|16:240</t>
   </si>
   <si>
     <t>24</t>
@@ -337,40 +343,40 @@
     <t>1:12|2:10|3:2.4</t>
   </si>
   <si>
-    <t>冥界亚龙</t>
-  </si>
-  <si>
-    <t>textures/heros/viper</t>
-  </si>
-  <si>
-    <t>1:380|2:160|3:28|4:120|16:220</t>
+    <t>哈斯卡</t>
+  </si>
+  <si>
+    <t>textures/heros/hasika</t>
+  </si>
+  <si>
+    <t>1:500|2:80|3:25|4:130|16:200</t>
   </si>
   <si>
     <t>27</t>
   </si>
   <si>
-    <t>venom</t>
-  </si>
-  <si>
-    <t>1:14|3:2.2</t>
-  </si>
-  <si>
-    <t>谜团</t>
-  </si>
-  <si>
-    <t>textures/heros/mituan</t>
-  </si>
-  <si>
-    <t>1:400|2:240|3:26|4:95|16:220</t>
+    <t>spear</t>
+  </si>
+  <si>
+    <t>1:20|3:2</t>
+  </si>
+  <si>
+    <t>骷髅王</t>
+  </si>
+  <si>
+    <t>textures/heros/kulouwang</t>
+  </si>
+  <si>
+    <t>1:460|2:200|3:24|4:95|16:210</t>
   </si>
   <si>
     <t>28</t>
   </si>
   <si>
-    <t>shadow</t>
-  </si>
-  <si>
-    <t>1:15|2:11|3:2</t>
+    <t>bone</t>
+  </si>
+  <si>
+    <t>1:15|3:2</t>
   </si>
   <si>
     <t>哥布林</t>
@@ -382,7 +388,7 @@
     <t>normal</t>
   </si>
   <si>
-    <t>1:40|2:30|5:70|3:0|4:100|6:0|7:25|16:44</t>
+    <t>1:40|2:30|5:70|3:4|4:100|6:0|7:25|16:44</t>
   </si>
   <si>
     <t>[]</t>
@@ -454,10 +460,10 @@
     <t>1:3000|2:300|5:140|3:60|4:80|6:12|7:35|16:180</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>{"type":"boss","params":{"skillInterval":6,"skillId":"fireball","phases":[{"hpRatio":1,"behavior":"chase","params":{"speedMul":0.8}},{"hpRatio":0.7,"behavior":"orbit","params":{"orbitRadius":150,"angularSpeed":1.2}},{"hpRatio":0.4,"behavior":"chase","params":{"speedMul":1.6}},{"hpRatio":0.2,"behavior":"attack_stop","params":{"stopDuration":1.2,"speedMul":1.8}}]}}</t>
+    <t>1,30,31</t>
+  </si>
+  <si>
+    <t>{"type":"boss","params":{"skills":[{"abilityId":1,"interval":6,"delay":3},{"abilityId":30,"interval":16,"delay":8,"hpBelow":0.65},{"abilityId":31,"interval":22,"delay":14,"hpBelow":0.35}],"phases":[{"hpRatio":1,"behavior":"chase","params":{"speedMul":0.8}},{"hpRatio":0.7,"behavior":"orbit","params":{"orbitRadius":150,"angularSpeed":1.2}},{"hpRatio":0.4,"behavior":"chase","params":{"speedMul":1.6}},{"hpRatio":0.2,"behavior":"attack_stop","params":{"stopDuration":1.2,"speedMul":1.8},"onEnterModifier":9,"onEnterDuration":8}]}}</t>
   </si>
   <si>
     <t>prefabs/units/monster_9</t>
@@ -484,7 +490,7 @@
     <t>exp_boss</t>
   </si>
   <si>
-    <t>{"type":"boss","params":{"skillInterval":8,"skillId":"sun_light","phases":[{"hpRatio":1,"behavior":"chase","params":{"speedMul":0.7}}]}}</t>
+    <t>{"type":"boss","params":{"skills":[{"abilityId":3,"interval":8,"delay":2,"selfCast":true}],"phases":[{"hpRatio":1,"behavior":"chase","params":{"speedMul":0.7}}]}}</t>
   </si>
   <si>
     <t>处刑者</t>
@@ -942,12 +948,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V23"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18.5" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="13.5" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
@@ -962,14 +968,15 @@
     <col min="15" max="15" width="10" customWidth="1"/>
     <col min="16" max="16" width="30" customWidth="1"/>
     <col min="17" max="17" width="29.5" customWidth="1"/>
-    <col min="18" max="18" width="31.5" customWidth="1"/>
-    <col min="19" max="19" width="60" customWidth="1"/>
-    <col min="20" max="20" width="18" customWidth="1"/>
-    <col min="21" max="21" width="27" customWidth="1"/>
-    <col min="22" max="22" width="36.5" customWidth="1"/>
+    <col min="18" max="18" width="60" customWidth="1"/>
+    <col min="19" max="19" width="31.5" customWidth="1"/>
+    <col min="20" max="20" width="60" customWidth="1"/>
+    <col min="21" max="21" width="18" customWidth="1"/>
+    <col min="22" max="22" width="27" customWidth="1"/>
+    <col min="23" max="23" width="36.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" ht="20" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1036,179 +1043,188 @@
       <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" ht="20" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="M2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="O2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="2" t="s">
+      <c r="T2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="V2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>29</v>
+      <c r="W2" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" ht="22" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1001</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D4" s="4">
         <v>1</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4">
         <v>1</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M4" s="4"/>
       <c r="N4" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O4" s="4">
         <v>0</v>
@@ -1217,38 +1233,39 @@
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
-      <c r="T4" s="4">
+      <c r="T4" s="4"/>
+      <c r="U4" s="4">
         <v>24</v>
       </c>
-      <c r="U4" s="4" t="s">
-        <v>60</v>
-      </c>
       <c r="V4" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>1002</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4">
@@ -1256,11 +1273,11 @@
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M5" s="4"/>
       <c r="N5" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O5" s="4">
         <v>0</v>
@@ -1269,38 +1286,39 @@
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="4">
+      <c r="T5" s="4"/>
+      <c r="U5" s="4">
         <v>26</v>
       </c>
-      <c r="U5" s="4" t="s">
-        <v>67</v>
-      </c>
       <c r="V5" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>1003</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D6" s="4">
         <v>1</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4">
@@ -1308,11 +1326,11 @@
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M6" s="4"/>
       <c r="N6" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O6" s="4">
         <v>0</v>
@@ -1321,38 +1339,39 @@
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
-      <c r="T6" s="4">
+      <c r="T6" s="4"/>
+      <c r="U6" s="4">
         <v>24</v>
       </c>
-      <c r="U6" s="4" t="s">
-        <v>74</v>
-      </c>
       <c r="V6" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="W6" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>1004</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D7" s="4">
         <v>1</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4">
@@ -1369,45 +1388,46 @@
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
-      <c r="T7" s="4">
+      <c r="T7" s="4"/>
+      <c r="U7" s="4">
         <v>30</v>
       </c>
-      <c r="U7" s="4" t="s">
-        <v>80</v>
-      </c>
       <c r="V7" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="W7" s="4" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>1005</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4">
         <v>1</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
@@ -1419,50 +1439,51 @@
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
       <c r="S8" s="4"/>
-      <c r="T8" s="4">
+      <c r="T8" s="4"/>
+      <c r="U8" s="4">
         <v>24</v>
       </c>
-      <c r="U8" s="4"/>
-      <c r="V8" s="4" t="s">
-        <v>87</v>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4" t="s">
+        <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>1006</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I9" s="4"/>
       <c r="J9" s="4">
         <v>0.9</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M9" s="4"/>
       <c r="N9" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O9" s="4">
         <v>0</v>
@@ -1471,50 +1492,51 @@
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
       <c r="S9" s="4"/>
-      <c r="T9" s="4">
+      <c r="T9" s="4"/>
+      <c r="U9" s="4">
         <v>24</v>
       </c>
-      <c r="U9" s="4"/>
-      <c r="V9" s="4" t="s">
-        <v>94</v>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>1007</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4">
         <v>1.3</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M10" s="4"/>
       <c r="N10" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O10" s="4">
         <v>0</v>
@@ -1523,50 +1545,51 @@
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
       <c r="S10" s="4"/>
-      <c r="T10" s="4">
+      <c r="T10" s="4"/>
+      <c r="U10" s="4">
         <v>26</v>
       </c>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4" t="s">
-        <v>100</v>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4" t="s">
+        <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>1008</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D11" s="4">
         <v>1</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4">
         <v>1.15</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M11" s="4"/>
       <c r="N11" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O11" s="4">
         <v>0</v>
@@ -1575,50 +1598,51 @@
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
       <c r="S11" s="4"/>
-      <c r="T11" s="4">
+      <c r="T11" s="4"/>
+      <c r="U11" s="4">
         <v>24</v>
       </c>
-      <c r="U11" s="4"/>
-      <c r="V11" s="4" t="s">
-        <v>107</v>
+      <c r="V11" s="4"/>
+      <c r="W11" s="4" t="s">
+        <v>109</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>1009</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M12" s="4"/>
       <c r="N12" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O12" s="4">
         <v>0</v>
@@ -1627,50 +1651,51 @@
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
       <c r="S12" s="4"/>
-      <c r="T12" s="4">
+      <c r="T12" s="4"/>
+      <c r="U12" s="4">
         <v>26</v>
       </c>
-      <c r="U12" s="4"/>
-      <c r="V12" s="4" t="s">
-        <v>113</v>
+      <c r="V12" s="4"/>
+      <c r="W12" s="4" t="s">
+        <v>115</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>1010</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D13" s="4">
         <v>1</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I13" s="4"/>
       <c r="J13" s="4">
         <v>1.35</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="M13" s="4"/>
       <c r="N13" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O13" s="4">
         <v>0</v>
@@ -1679,40 +1704,41 @@
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
       <c r="S13" s="4"/>
-      <c r="T13" s="4">
+      <c r="T13" s="4"/>
+      <c r="U13" s="4">
         <v>26</v>
       </c>
-      <c r="U13" s="4"/>
-      <c r="V13" s="4" t="s">
-        <v>119</v>
+      <c r="V13" s="4"/>
+      <c r="W13" s="4" t="s">
+        <v>121</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>2001</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4">
         <v>2</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1727,42 +1753,45 @@
       <c r="Q14" s="4">
         <v>8</v>
       </c>
-      <c r="R14" s="4" t="s">
-        <v>122</v>
+      <c r="R14" s="4">
+        <v>1</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="T14" s="4">
+        <v>124</v>
+      </c>
+      <c r="T14" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="U14" s="4">
         <v>10</v>
       </c>
-      <c r="U14" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="V14" s="4"/>
+      <c r="V14" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="W14" s="4"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>2002</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4">
         <v>2</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4">
@@ -1781,42 +1810,45 @@
       <c r="Q15" s="4">
         <v>15</v>
       </c>
-      <c r="R15" s="4" t="s">
-        <v>122</v>
+      <c r="R15" s="4">
+        <v>1</v>
       </c>
       <c r="S15" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="T15" s="4">
+        <v>124</v>
+      </c>
+      <c r="T15" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="U15" s="4">
         <v>24</v>
       </c>
-      <c r="U15" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="V15" s="4"/>
+      <c r="V15" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="W15" s="4"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>2003</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4">
         <v>2</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" s="4">
@@ -1835,42 +1867,45 @@
       <c r="Q16" s="4">
         <v>6</v>
       </c>
-      <c r="R16" s="4" t="s">
-        <v>122</v>
+      <c r="R16" s="4">
+        <v>1</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="T16" s="4">
+        <v>124</v>
+      </c>
+      <c r="T16" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="U16" s="4">
         <v>18</v>
       </c>
-      <c r="U16" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="V16" s="4"/>
+      <c r="V16" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="W16" s="4"/>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>2004</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4">
         <v>2</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I17" s="4"/>
       <c r="J17" s="4">
@@ -1889,42 +1924,45 @@
       <c r="Q17" s="4">
         <v>10</v>
       </c>
-      <c r="R17" s="4" t="s">
-        <v>122</v>
+      <c r="R17" s="4">
+        <v>1</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="T17" s="4">
+        <v>124</v>
+      </c>
+      <c r="T17" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="U17" s="4">
         <v>18</v>
       </c>
-      <c r="U17" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="V17" s="4"/>
+      <c r="V17" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="W17" s="4"/>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>2005</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4">
         <v>2</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I18" s="4"/>
       <c r="J18" s="4">
@@ -1943,42 +1981,45 @@
       <c r="Q18" s="4">
         <v>25</v>
       </c>
-      <c r="R18" s="4" t="s">
-        <v>140</v>
+      <c r="R18" s="4">
+        <v>1</v>
       </c>
       <c r="S18" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="T18" s="4">
+      <c r="T18" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="U18" s="4">
         <v>26</v>
       </c>
-      <c r="U18" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="V18" s="4"/>
+      <c r="V18" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="W18" s="4"/>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>2006</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4">
         <v>2</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I19" s="4"/>
       <c r="J19" s="4">
@@ -1997,42 +2038,45 @@
       <c r="Q19" s="4">
         <v>200</v>
       </c>
-      <c r="R19" s="4" t="s">
-        <v>145</v>
+      <c r="R19" s="4">
+        <v>1</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="T19" s="4">
+        <v>147</v>
+      </c>
+      <c r="T19" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="U19" s="4">
         <v>40</v>
       </c>
-      <c r="U19" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="V19" s="4"/>
+      <c r="V19" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="W19" s="4"/>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>2007</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4">
         <v>2</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4">
@@ -2051,42 +2095,45 @@
       <c r="Q20" s="4">
         <v>5</v>
       </c>
-      <c r="R20" s="4" t="s">
-        <v>152</v>
+      <c r="R20" s="4">
+        <v>1</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="T20" s="4">
+        <v>154</v>
+      </c>
+      <c r="T20" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="U20" s="4">
         <v>38</v>
       </c>
-      <c r="U20" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="V20" s="4"/>
+      <c r="V20" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="W20" s="4"/>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>2008</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4">
         <v>2</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I21" s="4"/>
       <c r="J21" s="4">
@@ -2105,42 +2152,45 @@
       <c r="Q21" s="4">
         <v>800</v>
       </c>
-      <c r="R21" s="4" t="s">
-        <v>156</v>
+      <c r="R21" s="4">
+        <v>1</v>
       </c>
       <c r="S21" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="T21" s="4">
+        <v>158</v>
+      </c>
+      <c r="T21" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="U21" s="4">
         <v>36</v>
       </c>
-      <c r="U21" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="V21" s="4"/>
+      <c r="V21" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="W21" s="4"/>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>2009</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4">
         <v>2</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I22" s="4"/>
       <c r="J22" s="4">
@@ -2159,42 +2209,45 @@
       <c r="Q22" s="4">
         <v>120</v>
       </c>
-      <c r="R22" s="4" t="s">
-        <v>160</v>
+      <c r="R22" s="4">
+        <v>150</v>
       </c>
       <c r="S22" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="T22" s="4">
+        <v>162</v>
+      </c>
+      <c r="T22" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="U22" s="4">
         <v>32</v>
       </c>
-      <c r="U22" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="V22" s="4"/>
+      <c r="V22" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="W22" s="4"/>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>2010</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="4">
         <v>2</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I23" s="4"/>
       <c r="J23" s="4">
@@ -2213,19 +2266,22 @@
       <c r="Q23" s="4">
         <v>200</v>
       </c>
-      <c r="R23" s="4" t="s">
-        <v>145</v>
+      <c r="R23" s="4">
+        <v>1</v>
       </c>
       <c r="S23" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="T23" s="4">
+        <v>147</v>
+      </c>
+      <c r="T23" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="U23" s="4">
         <v>48</v>
       </c>
-      <c r="U23" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="V23" s="4"/>
+      <c r="V23" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="W23" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="4">
@@ -2238,7 +2294,7 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="取值非法" error="只能是：nearest / farthest / lowest_hp / strongest / random" sqref="K4:K160">
       <formula1>"nearest,farthest,lowest_hp,strongest,random"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="取值非法" error="只能是：normal / elite / boss / gold_boss / exp_boss / kill_boss" sqref="R4:R160">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="取值非法" error="只能是：normal / elite / boss / gold_boss / exp_boss / kill_boss" sqref="S4:S160">
       <formula1>"normal,elite,boss,gold_boss,exp_boss,kill_boss"</formula1>
     </dataValidation>
   </dataValidations>

--- a/tools/excel_export/excel/units.xlsx
+++ b/tools/excel_export/excel/units.xlsx
@@ -1,17 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\cocos\jihe_defence\tools\excel_export\excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView windowWidth="27165" windowHeight="10845"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="units" state="visible" r:id="rId4"/>
+    <sheet name="units" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="168">
   <si>
     <t>id</t>
   </si>
@@ -509,43 +530,203 @@
   </si>
   <si>
     <t>1:1500|2:80|5:55|3:12|4:100|6:10|7:30|16:150</t>
+  </si>
+  <si>
+    <t>最终boss1</t>
+  </si>
+  <si>
+    <t>1:500000|2:300|5:140|3:60|4:80|6:100|7:90|16:180</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
       <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <i/>
+      <sz val="10"/>
       <color rgb="FF404040"/>
-      <sz val="10"/>
       <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF404040"/>
-      <sz val="10"/>
       <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -555,20 +736,203 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E79"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDCE6F1"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -591,9 +955,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -610,17 +1216,61 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -942,14 +1592,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W23"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:W24"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18.5" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -976,7 +1626,7 @@
     <col min="23" max="23" width="36.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" ht="20" customHeight="1" spans="1:23">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1047,7 +1697,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" ht="20" customHeight="1" spans="1:23">
       <c r="A2" s="2" t="s">
         <v>23</v>
       </c>
@@ -1118,7 +1768,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" ht="22" customHeight="1" spans="1:23">
       <c r="A3" s="3" t="s">
         <v>31</v>
       </c>
@@ -1189,7 +1839,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" ht="16.5" spans="1:23">
       <c r="A4" s="4">
         <v>1001</v>
       </c>
@@ -1244,7 +1894,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" ht="16.5" spans="1:23">
       <c r="A5" s="4">
         <v>1002</v>
       </c>
@@ -1297,7 +1947,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" ht="16.5" spans="1:23">
       <c r="A6" s="4">
         <v>1003</v>
       </c>
@@ -1350,7 +2000,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" ht="16.5" spans="1:23">
       <c r="A7" s="4">
         <v>1004</v>
       </c>
@@ -1399,7 +2049,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" ht="16.5" spans="1:23">
       <c r="A8" s="4">
         <v>1005</v>
       </c>
@@ -1448,7 +2098,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" ht="16.5" spans="1:23">
       <c r="A9" s="4">
         <v>1006</v>
       </c>
@@ -1501,7 +2151,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.5" spans="1:23">
       <c r="A10" s="4">
         <v>1007</v>
       </c>
@@ -1554,7 +2204,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.5" spans="1:23">
       <c r="A11" s="4">
         <v>1008</v>
       </c>
@@ -1607,7 +2257,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" ht="16.5" spans="1:23">
       <c r="A12" s="4">
         <v>1009</v>
       </c>
@@ -1660,7 +2310,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="13" ht="16.5" spans="1:23">
       <c r="A13" s="4">
         <v>1010</v>
       </c>
@@ -1713,7 +2363,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" ht="16.5" spans="1:23">
       <c r="A14" s="4">
         <v>2001</v>
       </c>
@@ -1770,7 +2420,7 @@
       </c>
       <c r="W14" s="4"/>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" ht="16.5" spans="1:23">
       <c r="A15" s="4">
         <v>2002</v>
       </c>
@@ -1827,7 +2477,7 @@
       </c>
       <c r="W15" s="4"/>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" ht="16.5" spans="1:23">
       <c r="A16" s="4">
         <v>2003</v>
       </c>
@@ -1884,7 +2534,7 @@
       </c>
       <c r="W16" s="4"/>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="17" ht="16.5" spans="1:23">
       <c r="A17" s="4">
         <v>2004</v>
       </c>
@@ -1941,7 +2591,7 @@
       </c>
       <c r="W17" s="4"/>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="18" ht="16.5" spans="1:23">
       <c r="A18" s="4">
         <v>2005</v>
       </c>
@@ -1998,7 +2648,7 @@
       </c>
       <c r="W18" s="4"/>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="19" ht="16.5" spans="1:23">
       <c r="A19" s="4">
         <v>2006</v>
       </c>
@@ -2055,7 +2705,7 @@
       </c>
       <c r="W19" s="4"/>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="20" ht="16.5" spans="1:23">
       <c r="A20" s="4">
         <v>2007</v>
       </c>
@@ -2112,7 +2762,7 @@
       </c>
       <c r="W20" s="4"/>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="21" ht="16.5" spans="1:23">
       <c r="A21" s="4">
         <v>2008</v>
       </c>
@@ -2169,7 +2819,7 @@
       </c>
       <c r="W21" s="4"/>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="22" ht="16.5" spans="1:23">
       <c r="A22" s="4">
         <v>2009</v>
       </c>
@@ -2226,7 +2876,7 @@
       </c>
       <c r="W22" s="4"/>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="23" ht="16.5" spans="1:23">
       <c r="A23" s="4">
         <v>2010</v>
       </c>
@@ -2282,6 +2932,63 @@
         <v>151</v>
       </c>
       <c r="W23" s="4"/>
+    </row>
+    <row r="24" ht="16.5" spans="1:23">
+      <c r="A24" s="4">
+        <v>2011</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4">
+        <v>2</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4">
+        <v>500</v>
+      </c>
+      <c r="P24" s="4">
+        <v>40</v>
+      </c>
+      <c r="Q24" s="4">
+        <v>200</v>
+      </c>
+      <c r="R24" s="4">
+        <v>1</v>
+      </c>
+      <c r="S24" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="T24" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="U24" s="4">
+        <v>40</v>
+      </c>
+      <c r="V24" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="W24" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="4">
@@ -2299,6 +3006,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>